--- a/output/260722__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260722__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/287f5y34</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016207102?sid=102</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2d72joxa</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004643754?sid=102</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24fwrxdg</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009071466?sid=102</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29fk8nam</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003038158?sid=102</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28l5s8gl</t>
+          <t>https://n.news.naver.com/mnews/article/422/0000887462?sid=102</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xl3a63w</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000628394?sid=102</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2akb6zvb</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012222492?sid=102</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2c97xfjd</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382665?sid=102</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
+          <t>[한겨레] 우원식 “민주당, 양극화 토론 한번을 안 해…중산층·서민 정당 맞나”</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/234dhhj2</t>
+          <t>https://n.news.naver.com/mnews/article/028/0002815160?sid=100</t>
         </is>
       </c>
     </row>
@@ -596,43 +596,43 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyrxdhg</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004170634?sid=100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
+          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29c62tnq</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003663208?sid=100</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
+          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/257xylkl</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014079773?sid=102</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 김민석, ‘신천지 전대 개입설’ 제기… 정청래 “황당한 네거티브”</t>
+          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23z47owj</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014079777?sid=100</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] '명태균 여론조사 대납' 오세훈 1심 선고… 구형은 징역 1년6개월</t>
+          <t>[머니투데이] 오세훈, 여론조사 대납 1심 선고 '운명의 날'…구형은 '시장직 박탈형'</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27geucsw</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388961?sid=102</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2ar6z653</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003038151?sid=100</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25rj3g7u</t>
+          <t>https://n.news.naver.com/mnews/article/661/0000080295?sid=100</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25x4nydt</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517842?sid=100</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2b7u8dzk</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517843?sid=100</t>
         </is>
       </c>
     </row>
@@ -718,19 +718,19 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2233pfz9</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000943610?sid=101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] [단독]'따릉이 정보유출' 대형사고에도…서울시설공단 이사장 연임 논란</t>
+          <t>[이데일리] [단독]'따릉이 정보유출'에도…서울시설공단 이사장 연임 논란</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2adfrvoj</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006334250?sid=100</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2c7ge29f</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735595?sid=102</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24asyqgm</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001862350?sid=101</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29afggds</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517840?sid=100</t>
         </is>
       </c>
     </row>

--- a/output/260722__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260722__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016207102?sid=102</t>
+          <t>https://n.news.naver.com/article/001/0016207102</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004643754?sid=102</t>
+          <t>https://n.news.naver.com/article/011/0004643754</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009071466?sid=102</t>
+          <t>https://n.news.naver.com/article/421/0009071466</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003038158?sid=102</t>
+          <t>https://n.news.naver.com/article/029/0003038158</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000887462?sid=102</t>
+          <t>https://n.news.naver.com/article/422/0000887462</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000628394?sid=102</t>
+          <t>https://n.news.naver.com/article/448/0000628394</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012222492?sid=102</t>
+          <t>https://n.news.naver.com/article/056/0012222492</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382665?sid=102</t>
+          <t>https://n.news.naver.com/article/052/0002382665</t>
         </is>
       </c>
     </row>
@@ -584,55 +584,55 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/028/0002815160?sid=100</t>
+          <t>https://n.news.naver.com/article/028/0002815160</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 김민석은 왜 '신천지'를 언급할까…숨겨진 전략은</t>
+          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170634?sid=100</t>
+          <t>https://n.news.naver.com/article/081/0003663208</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
+          <t>[노컷뉴스] 김민석은 왜 '신천지'를 언급할까…숨겨진 전략은</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003663208?sid=100</t>
+          <t>https://n.news.naver.com/article/079/0004170634</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
+          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014079773?sid=102</t>
+          <t>https://n.news.naver.com/article/003/0014079777</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
+          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014079777?sid=100</t>
+          <t>https://n.news.naver.com/article/003/0014079773</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388961?sid=102</t>
+          <t>https://n.news.naver.com/article/008/0005388961</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003038151?sid=100</t>
+          <t>https://n.news.naver.com/article/029/0003038151</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/661/0000080295?sid=100</t>
+          <t>https://n.news.naver.com/article/661/0000080295</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517842?sid=100</t>
+          <t>https://n.news.naver.com/article/629/0000517842</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517843?sid=100</t>
+          <t>https://n.news.naver.com/article/629/0000517843</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943610?sid=101</t>
+          <t>https://n.news.naver.com/article/469/0000943610</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006334250?sid=100</t>
+          <t>https://n.news.naver.com/article/018/0006334250</t>
         </is>
       </c>
     </row>
@@ -742,31 +742,31 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735595?sid=102</t>
+          <t>https://n.news.naver.com/article/020/0003735595</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] “AI로 2030 다시 잡아라”… ‘국민 첫 차’ 아반떼 재시동</t>
+          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001862350?sid=101</t>
+          <t>https://n.news.naver.com/article/629/0000517840</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
+          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517840?sid=100</t>
+          <t>https://n.news.naver.com/article/008/0005388944</t>
         </is>
       </c>
     </row>

--- a/output/260722__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260722__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -749,24 +749,24 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
+          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000517840</t>
+          <t>https://n.news.naver.com/article/008/0005388944</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
+          <t>[머니투데이] "하녀처럼 부리던 여교사 구타" 췌장 파열→사망...종교인 탈 쓴 악마 짓...</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005388944</t>
+          <t>https://n.news.naver.com/article/008/0005388976</t>
         </is>
       </c>
     </row>
